--- a/questions_answers.xlsx
+++ b/questions_answers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\chataddb\stubot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B44A1B98-2E22-4094-BE96-F12612DD7C0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{780D9CDD-DB76-4AB6-9ACC-8C17C2764D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1DAF3C1D-9B04-428E-B9FE-47A514BA530F}"/>
   </bookViews>

--- a/questions_answers.xlsx
+++ b/questions_answers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\chataddb\stubot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{780D9CDD-DB76-4AB6-9ACC-8C17C2764D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13BE31B3-249D-42A0-99E1-62D17CDF37A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1DAF3C1D-9B04-428E-B9FE-47A514BA530F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>question</t>
   </si>
@@ -138,31 +138,34 @@
     <t xml:space="preserve">Nowadays, getting job is quite tough. So, try to retain the first job as long as you can. Learn the skills, processes, system, understand the working culture. This will enhance your professional abilities &amp; skills to get a proper growth in your career. </t>
   </si>
   <si>
-    <t>What kind of job role he/she aspires to?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	Questions to check background of the candidates (like family background, last qualification etc)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	Willing to do job?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	Willing to relocate or not? If yes then preferences of locations.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	As most of the job locations are Kolkata surroundings therefore is he okay with the distance? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">	Willing to do rotational Shift?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	Expected Salary as a fresher? We do have a salary range set for positions as fresher. Is the candidate okay with that? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">	Is the candidate okay with the class timings/attendance percentage set by Anudip parameters to be able to get placement benefits? </t>
-  </si>
-  <si>
-    <t>Test Question</t>
+    <t>What kind of job role you aspire to?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is your family background ? </t>
+  </si>
+  <si>
+    <t>What is your educational qualification ?</t>
+  </si>
+  <si>
+    <t>Are you willing to do job?</t>
+  </si>
+  <si>
+    <t>Willing to relocate or not?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	As most of the job locations are bit far away from your current location therefore are you okay with the distance? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Are you willing to do rotational shift?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	What is your expected Salary as a fresher?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Are you okay with the class timings as attendance percentage set by Anudip parameters to be able to get placement benefits? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is your family income ? </t>
   </si>
 </sst>
 </file>
@@ -515,10 +518,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6DEF95E-08A4-4BEB-913A-99C70BCF58D5}">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="113.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="79.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.36328125" bestFit="1" customWidth="1"/>
   </cols>
@@ -671,7 +674,7 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.35">
@@ -681,36 +684,41 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+      <c r="A20" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>37</v>
+      <c r="A21" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>41</v>
       </c>
     </row>

--- a/questions_answers.xlsx
+++ b/questions_answers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\chataddb\stubot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13BE31B3-249D-42A0-99E1-62D17CDF37A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10FFB06B-3072-4657-9755-D83B7777B66E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1DAF3C1D-9B04-428E-B9FE-47A514BA530F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>question</t>
   </si>
@@ -166,6 +166,9 @@
   </si>
   <si>
     <t xml:space="preserve">What is your family income ? </t>
+  </si>
+  <si>
+    <t>Test Question(For Only Test)</t>
   </si>
 </sst>
 </file>
@@ -518,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6DEF95E-08A4-4BEB-913A-99C70BCF58D5}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="113.1796875" bestFit="1" customWidth="1"/>
@@ -722,6 +725,11 @@
         <v>41</v>
       </c>
     </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/questions_answers.xlsx
+++ b/questions_answers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\chataddb\stubot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10FFB06B-3072-4657-9755-D83B7777B66E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4038F316-BD57-44CB-A9C2-D21A35101525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1DAF3C1D-9B04-428E-B9FE-47A514BA530F}"/>
   </bookViews>

--- a/questions_answers.xlsx
+++ b/questions_answers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\chataddb\stubot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4038F316-BD57-44CB-A9C2-D21A35101525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D42F8DB-D7A0-400F-A79C-5C1CD7FB5984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1DAF3C1D-9B04-428E-B9FE-47A514BA530F}"/>
   </bookViews>
@@ -66,12 +66,6 @@
     <t>Yes, you will get the study material related to your course from Anudip.</t>
   </si>
   <si>
-    <t>What is the mark to pass the examination?</t>
-  </si>
-  <si>
-    <t>The minimum pass mark is 50. According to your marks the grade will be reflected on your certificate. (Less than or equals to 49- F, 50-59= D, 60-69= C, 70-79= B, 80-89=A &amp; 90-100= A+)</t>
-  </si>
-  <si>
     <t>How many days it will take to conduct the final examination after completion of the course?</t>
   </si>
   <si>
@@ -169,6 +163,12 @@
   </si>
   <si>
     <t>Test Question(For Only Test)</t>
+  </si>
+  <si>
+    <t>The minimum passing number is 50. According to your number the grade will be reflected on your certificate. (Less than or equals to 49- F, 50-59= D, 60-69= C, 70-79= B, 80-89=A &amp; 90-100= A+)</t>
+  </si>
+  <si>
+    <t>What is the passing number in  the examination?</t>
   </si>
 </sst>
 </file>
@@ -569,165 +569,165 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C8" s="1"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C9" s="1"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C10" s="1"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C11" s="1"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C12" s="1"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C13" s="1"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C14" s="1"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C15" s="1"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C16" s="1"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/questions_answers.xlsx
+++ b/questions_answers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\chataddb\stubot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D42F8DB-D7A0-400F-A79C-5C1CD7FB5984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DBCB3D5-6FE5-41CA-A9AA-8F07101BFB80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1DAF3C1D-9B04-428E-B9FE-47A514BA530F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>question</t>
   </si>
@@ -169,6 +169,60 @@
   </si>
   <si>
     <t>What is the passing number in  the examination?</t>
+  </si>
+  <si>
+    <t>What kind of support does Anudip offer after I get placed?</t>
+  </si>
+  <si>
+    <t>Anudip offers post-placement follow-ups, guidance for workplace adaptation, and alumni networking opportunities</t>
+  </si>
+  <si>
+    <t>Does Anudip offer any courses in regional languages like Bengali or Hindi?</t>
+  </si>
+  <si>
+    <t>Yes, basic instructions and mentoring are available in regional languages, but digital and soft skill modules are predominantly in English to build employability.</t>
+  </si>
+  <si>
+    <t>I am a person with a disability. Does Anudip have support for me?</t>
+  </si>
+  <si>
+    <t>Yes, Anudip is an inclusive organization. Please contact the Centre Faculty to enquire if there are relevant courses operational for PWD youths.</t>
+  </si>
+  <si>
+    <t>What if I face technical issues logging into online sessions?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Please contact the faculty for guidance </t>
+  </si>
+  <si>
+    <t>Will I receive a certificate after completing the course?</t>
+  </si>
+  <si>
+    <t>Yes, a certificate is issued after successful course completion and internal assessment, usually within 15–30 working days. You are encouraged to collect it from your training centre</t>
+  </si>
+  <si>
+    <t>How does Anudip ensure job placements are genuine and safe?</t>
+  </si>
+  <si>
+    <t>All placement partners are verified through a due diligence process, and job offers are tracked for compliance, salary standards, and safety.</t>
+  </si>
+  <si>
+    <t>Can I refer a friend or sibling to enroll in Anudip’s courses?</t>
+  </si>
+  <si>
+    <t>Yes, referrals are welcome. Your friend can apply by walking in to his/her nearest Anudip training centre</t>
+  </si>
+  <si>
+    <t>How can I become part of the Anudip Alumni Network?</t>
+  </si>
+  <si>
+    <t>All placed candidates are encouraged to join Anudip Alumni Network in social media. Please reach out to your faculty for guidance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What if my concern is not listed here ? </t>
+  </si>
+  <si>
+    <t>If your concern is not listed please contact your faculty for any concern/support/guidance</t>
   </si>
 </sst>
 </file>
@@ -521,7 +575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6DEF95E-08A4-4BEB-913A-99C70BCF58D5}">
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="113.1796875" bestFit="1" customWidth="1"/>
@@ -675,58 +729,130 @@
       </c>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A19" s="1" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
         <v>41</v>
       </c>
     </row>

--- a/questions_answers.xlsx
+++ b/questions_answers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\chataddb\stubot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DBCB3D5-6FE5-41CA-A9AA-8F07101BFB80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B456E67-CBFC-4DC5-A7D5-1A1B7FAAE138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1DAF3C1D-9B04-428E-B9FE-47A514BA530F}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$35</definedName>
     <definedName name="OLE_LINK2" localSheetId="0">Sheet1!$A$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>question</t>
   </si>
@@ -76,12 +77,6 @@
   </si>
   <si>
     <t>Tentatively it will take 45-60 days after examination to get the certificate.</t>
-  </si>
-  <si>
-    <t>Can we get the certificate from NSDC?</t>
-  </si>
-  <si>
-    <t>In some courses we have provision for NSDC certification along with Anudip certificate.</t>
   </si>
   <si>
     <t>Will we get only one certificate from Anudip?</t>
@@ -575,7 +570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6DEF95E-08A4-4BEB-913A-99C70BCF58D5}">
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="113.1796875" bestFit="1" customWidth="1"/>
@@ -623,10 +618,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C5" s="1"/>
     </row>
@@ -721,13 +716,12 @@
       <c r="C15" s="1"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="1"/>
+      <c r="A16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
@@ -794,56 +788,53 @@
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>60</v>
-      </c>
-      <c r="B25" t="s">
-        <v>61</v>
+      <c r="A25" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" s="1" t="s">
-        <v>31</v>
+      <c r="A30" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.35">
@@ -851,12 +842,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>41</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:C35" xr:uid="{A6DEF95E-08A4-4BEB-913A-99C70BCF58D5}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/questions_answers.xlsx
+++ b/questions_answers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\chataddb\stubot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B456E67-CBFC-4DC5-A7D5-1A1B7FAAE138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD8DA58B-BFE4-4B74-977C-B7FD7A992DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1DAF3C1D-9B04-428E-B9FE-47A514BA530F}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$37</definedName>
     <definedName name="OLE_LINK2" localSheetId="0">Sheet1!$A$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="63">
   <si>
     <t>question</t>
   </si>
@@ -106,15 +106,9 @@
     <t>Will I get the mock interview session in our centre?</t>
   </si>
   <si>
-    <t>Yes, you will definitely get the mock interview session in your centre. Your trainer will conduct the session.</t>
-  </si>
-  <si>
     <t>What will be the salary package I get as a fresher?</t>
   </si>
   <si>
-    <t xml:space="preserve">The salary package will always depend on the company &amp; the profile you are being selected for. </t>
-  </si>
-  <si>
     <t>In case of relocation can we get the facility of accommodation?</t>
   </si>
   <si>
@@ -160,9 +154,6 @@
     <t>Test Question(For Only Test)</t>
   </si>
   <si>
-    <t>The minimum passing number is 50. According to your number the grade will be reflected on your certificate. (Less than or equals to 49- F, 50-59= D, 60-69= C, 70-79= B, 80-89=A &amp; 90-100= A+)</t>
-  </si>
-  <si>
     <t>What is the passing number in  the examination?</t>
   </si>
   <si>
@@ -218,6 +209,24 @@
   </si>
   <si>
     <t>If your concern is not listed please contact your faculty for any concern/support/guidance</t>
+  </si>
+  <si>
+    <t>The minimum passing number is 50. According to your number the grade will be reflected on your certificate. (Less than or equals to 49 to F, 50 to 59= D, 60 to 69= C, 70 to 79= B, 80 to 89=A &amp; 90 to 100= A+)</t>
+  </si>
+  <si>
+    <t>All our learning content is available on Learning Management System</t>
+  </si>
+  <si>
+    <t>The salary package will always depend on the company &amp; the profile you are being selected for. Regular sessions will be conducted by placement manager during the training period for awareness about various job opperchunities covering Salary , Nature of work, Location etc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, you will definitely get the mock interview session in your centre. Your placement Manager will facilitate through our industry partner or byself. </t>
+  </si>
+  <si>
+    <t>What would be eligibility criteria for final assessment and to start with placement ?</t>
+  </si>
+  <si>
+    <t>Overall course Level attendance %age &gt;= 60%, All self learning assessment / assignment completion on LMS</t>
   </si>
 </sst>
 </file>
@@ -570,7 +579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6DEF95E-08A4-4BEB-913A-99C70BCF58D5}">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="113.1796875" bestFit="1" customWidth="1"/>
@@ -618,10 +627,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="C5" s="1"/>
     </row>
@@ -684,166 +693,182 @@
         <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="C12" s="1"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="C13" s="1"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C14" s="1"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C15" s="1"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" t="s">
         <v>58</v>
       </c>
-      <c r="B24" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" s="1" t="s">
-        <v>31</v>
-      </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" s="1" t="s">
-        <v>30</v>
+      <c r="A26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>33</v>
+      <c r="A30" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>34</v>
+      <c r="A31" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C35" xr:uid="{A6DEF95E-08A4-4BEB-913A-99C70BCF58D5}"/>
+  <autoFilter ref="A1:C37" xr:uid="{A6DEF95E-08A4-4BEB-913A-99C70BCF58D5}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/questions_answers.xlsx
+++ b/questions_answers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\chataddb\stubot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD8DA58B-BFE4-4B74-977C-B7FD7A992DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F192728A-7A13-4AE1-827C-5343A5CDDBFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1DAF3C1D-9B04-428E-B9FE-47A514BA530F}"/>
   </bookViews>
@@ -211,9 +211,6 @@
     <t>If your concern is not listed please contact your faculty for any concern/support/guidance</t>
   </si>
   <si>
-    <t>The minimum passing number is 50. According to your number the grade will be reflected on your certificate. (Less than or equals to 49 to F, 50 to 59= D, 60 to 69= C, 70 to 79= B, 80 to 89=A &amp; 90 to 100= A+)</t>
-  </si>
-  <si>
     <t>All our learning content is available on Learning Management System</t>
   </si>
   <si>
@@ -227,6 +224,9 @@
   </si>
   <si>
     <t>Overall course Level attendance %age &gt;= 60%, All self learning assessment / assignment completion on LMS</t>
+  </si>
+  <si>
+    <t>The minimum passing number is 50. According to your number the grade will be reflected on your certificate,Less than or equals to 49 to F, 50 to 59= D, 60 to 69= C, 70 to 79= B, 80 to 89=A &amp; 90 to 100= A+</t>
   </si>
 </sst>
 </file>
@@ -630,7 +630,7 @@
         <v>38</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C5" s="1"/>
     </row>
@@ -693,7 +693,7 @@
         <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C12" s="1"/>
     </row>
@@ -702,7 +702,7 @@
         <v>22</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C13" s="1"/>
     </row>
@@ -801,15 +801,15 @@
         <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" t="s">
         <v>61</v>
-      </c>
-      <c r="B26" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">

--- a/questions_answers.xlsx
+++ b/questions_answers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\chataddb\stubot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F192728A-7A13-4AE1-827C-5343A5CDDBFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1456C736-12B1-45A6-A133-DB92C4515E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1DAF3C1D-9B04-428E-B9FE-47A514BA530F}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="109">
   <si>
     <t>question</t>
   </si>
@@ -49,15 +49,9 @@
     <t>picpath</t>
   </si>
   <si>
-    <t>What is the course module ?</t>
-  </si>
-  <si>
     <t>That depends upon the course in which you are being enrolled. For any further information please communicate with your trainer.</t>
   </si>
   <si>
-    <t>Can we choose the mode of our classes by ourselves (Online/ Offline)?</t>
-  </si>
-  <si>
     <t xml:space="preserve"> If there is any Hybrid mode option (Online &amp; Offline) is available in your centre then you might get a chance to choose the mode. Please communicate with your trainer regarding it.</t>
   </si>
   <si>
@@ -67,9 +61,6 @@
     <t>Yes, you will get the study material related to your course from Anudip.</t>
   </si>
   <si>
-    <t>How many days it will take to conduct the final examination after completion of the course?</t>
-  </si>
-  <si>
     <t>Tentatively it will take 7-10 days after completion of the course to conduct the final examination.</t>
   </si>
   <si>
@@ -79,36 +70,18 @@
     <t>Tentatively it will take 45-60 days after examination to get the certificate.</t>
   </si>
   <si>
-    <t>Will we get only one certificate from Anudip?</t>
-  </si>
-  <si>
     <t>There are also some specific courses which are eligible for mettl assessment. If you are being enrolled for that very course then you will get a chance to attempt the exam &amp; after completion of your exam will get the both certificate from Anudip &amp; Mettl.</t>
   </si>
   <si>
-    <t xml:space="preserve">From where I should get the certificate? </t>
-  </si>
-  <si>
     <t>You will get your certificate from your respective centre.</t>
   </si>
   <si>
-    <t>Will I get the job opportunity on my domain?</t>
-  </si>
-  <si>
     <t>You will get various types of opportunities from Anudip. You can take the guidance from your trainer to choose the job.</t>
   </si>
   <si>
-    <t>Can we get the opportunity of work from home?</t>
-  </si>
-  <si>
     <t xml:space="preserve">If there is any specific requirement for Work from Home from any employer then you may get this opportunity. </t>
   </si>
   <si>
-    <t>Will I get the mock interview session in our centre?</t>
-  </si>
-  <si>
-    <t>What will be the salary package I get as a fresher?</t>
-  </si>
-  <si>
     <t>In case of relocation can we get the facility of accommodation?</t>
   </si>
   <si>
@@ -154,9 +127,6 @@
     <t>Test Question(For Only Test)</t>
   </si>
   <si>
-    <t>What is the passing number in  the examination?</t>
-  </si>
-  <si>
     <t>What kind of support does Anudip offer after I get placed?</t>
   </si>
   <si>
@@ -169,15 +139,9 @@
     <t>Yes, basic instructions and mentoring are available in regional languages, but digital and soft skill modules are predominantly in English to build employability.</t>
   </si>
   <si>
-    <t>I am a person with a disability. Does Anudip have support for me?</t>
-  </si>
-  <si>
     <t>Yes, Anudip is an inclusive organization. Please contact the Centre Faculty to enquire if there are relevant courses operational for PWD youths.</t>
   </si>
   <si>
-    <t>What if I face technical issues logging into online sessions?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Please contact the faculty for guidance </t>
   </si>
   <si>
@@ -199,9 +163,6 @@
     <t>Yes, referrals are welcome. Your friend can apply by walking in to his/her nearest Anudip training centre</t>
   </si>
   <si>
-    <t>How can I become part of the Anudip Alumni Network?</t>
-  </si>
-  <si>
     <t>All placed candidates are encouraged to join Anudip Alumni Network in social media. Please reach out to your faculty for guidance</t>
   </si>
   <si>
@@ -214,19 +175,196 @@
     <t>All our learning content is available on Learning Management System</t>
   </si>
   <si>
-    <t>The salary package will always depend on the company &amp; the profile you are being selected for. Regular sessions will be conducted by placement manager during the training period for awareness about various job opperchunities covering Salary , Nature of work, Location etc.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Yes, you will definitely get the mock interview session in your centre. Your placement Manager will facilitate through our industry partner or byself. </t>
   </si>
   <si>
-    <t>What would be eligibility criteria for final assessment and to start with placement ?</t>
-  </si>
-  <si>
     <t>Overall course Level attendance %age &gt;= 60%, All self learning assessment / assignment completion on LMS</t>
   </si>
   <si>
     <t>The minimum passing number is 50. According to your number the grade will be reflected on your certificate,Less than or equals to 49 to F, 50 to 59= D, 60 to 69= C, 70 to 79= B, 80 to 89=A &amp; 90 to 100= A+</t>
+  </si>
+  <si>
+    <t>What are the courses available at Anudip?</t>
+  </si>
+  <si>
+    <t>What is the mode of training (Online/Offline/Hybrid)?</t>
+  </si>
+  <si>
+    <t>May I get the self-study materials from the center once I get enrolled in the course?</t>
+  </si>
+  <si>
+    <t>What is the pass marks in the assessment?</t>
+  </si>
+  <si>
+    <t>The minimum passing number is 50. According to your number the grade will be reflected on your certificate,Less than or equals to 49 = F, 50 to 59= D, 60 to 69= C, 70 to 79= B, 80 to 89=A &amp; 90 to 100= A+</t>
+  </si>
+  <si>
+    <t>How many days it will take to conduct the final exam after the completion of the course?</t>
+  </si>
+  <si>
+    <t>Will I get only one certificate from Anudip?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From where I could get the certificate? </t>
+  </si>
+  <si>
+    <t>Will I be able to get the job opportunity on my domain?</t>
+  </si>
+  <si>
+    <t>Will I be able to get the opportunity of work from home?</t>
+  </si>
+  <si>
+    <t>Will I be able to get the mock interview session in our centre?</t>
+  </si>
+  <si>
+    <t>What will be the approx salary package if I get the opportunity as a fresher?</t>
+  </si>
+  <si>
+    <t>The salary package will always depend on the company &amp; the profile you are being selected for. Regular sessions will be conducted by placement manager during the training period for awareness about various job opportunities covering Salary , Nature of work, Location etc.</t>
+  </si>
+  <si>
+    <t>I am a specially abled person. Does Anudip have any extra support for me?</t>
+  </si>
+  <si>
+    <t>What if I face any technical issues during the online sessions?</t>
+  </si>
+  <si>
+    <t>How can I become a part of the Anudip Alumni Network?</t>
+  </si>
+  <si>
+    <t>What would be the eligibility criteria to appear the final assessment and to start with placement ?</t>
+  </si>
+  <si>
+    <t>Can you please provide me the Email ID &amp; Contact number of Anudip?</t>
+  </si>
+  <si>
+    <t>Yes, you can get the email ID &amp; contact number of Anudip through Anudip's official website anudip.org</t>
+  </si>
+  <si>
+    <t>What kind of courses are available at Anudip?</t>
+  </si>
+  <si>
+    <t>There are various types of courses running at Anudip centres from basic to high-end. Basic courses like Certificate in Sales Operation, Certificate in English communication &amp; IT etc. and high-end courses like Advanced Program in System Administrator, Cyber Security &amp; Ethical hacking etc. You will get the entire course modules from the official website.</t>
+  </si>
+  <si>
+    <t>What is the duration of the courses?</t>
+  </si>
+  <si>
+    <t>Could I get enrolled in more than one course at a time?</t>
+  </si>
+  <si>
+    <t>No, you have to complete the course in which you are being enrolled. After three months of your course completion you can get enrolled for another course.</t>
+  </si>
+  <si>
+    <t>Is there any minimum attendance required for certification and placement?</t>
+  </si>
+  <si>
+    <t>There is a minimum requirement of 60% or above attendance for certification &amp; placement.</t>
+  </si>
+  <si>
+    <t>Can I also get soft skill training along with the course I enrolled for?</t>
+  </si>
+  <si>
+    <t>Yes, you can get the soft skill training support with almost all the courses available at Anudip.</t>
+  </si>
+  <si>
+    <t>How does Anudip evaluate training effectiveness during the course?</t>
+  </si>
+  <si>
+    <t>Anudip evaluates training effectiveness during the course through participant feedback, observation, interactive activities, and ongoing assessments like quizzes and skill demonstrations. This helps trainers adjust content and methods in real-time to ensure learning objectives are being met.</t>
+  </si>
+  <si>
+    <t>What are the modules covered in the training?</t>
+  </si>
+  <si>
+    <t>You will get the internal learning management system from the centre. Based on your course structure you can get the modules here.</t>
+  </si>
+  <si>
+    <t>Are the classes live or recorded?</t>
+  </si>
+  <si>
+    <t>Basically the classes are live. But for online classes some sessions are being recorded for further requirment.</t>
+  </si>
+  <si>
+    <t>What happens if I miss a session?</t>
+  </si>
+  <si>
+    <t>If you miss a session then you can get the recorded classes from your respective trainer. But it depends on the availibility of recordings. In case of unavailibility you have to ask your trainer to brief the previous class again.</t>
+  </si>
+  <si>
+    <t>What is the exam/assessment process at Anudip?</t>
+  </si>
+  <si>
+    <t>We have two assessment partners. One is external &amp; another is internal. External is Mettl &amp; Internal is LMS. Fro LMS you will get the link from our internal LMS team. If you have done the exam through Mettl then you will get the link from Mettle directly.</t>
+  </si>
+  <si>
+    <t>What is the grading pattern in the assessments/examinations?</t>
+  </si>
+  <si>
+    <t>How can I check the authenticity of a certificate?</t>
+  </si>
+  <si>
+    <t>To check the authenticity of a certificate, verify it directly with the issuing institution through official website, email, or verification portal. Additionally, examine the certificate for security features like logo, QR codes, official seals, or signatures.</t>
+  </si>
+  <si>
+    <t>How do I download the course completion certificate?</t>
+  </si>
+  <si>
+    <t>After completion of your course if you pass the exam then you will get the certificate from your respective centre.</t>
+  </si>
+  <si>
+    <t>What if I lose my certificate?</t>
+  </si>
+  <si>
+    <t>If you lose your certificate then you can reapply for the duplicate certificate with the help of your trainer.</t>
+  </si>
+  <si>
+    <t>Will I be able to get the placement support after completion of training and assessments?</t>
+  </si>
+  <si>
+    <t>Obviously, as we provide livelihood to the students so that we have the responsibility to support you with the Placement opportunities.</t>
+  </si>
+  <si>
+    <t>Will I be able to get placement support if I complete the course but not the exam?</t>
+  </si>
+  <si>
+    <t>As you know if you do not appear for the final assessment test then you will not be able to get the certificate. So that it will be better to take the final assessment at first &amp; after that you will get the placement opportunities. Additionally in an immediate basis you can join the job but you need to take the final assessment as per trainer's insturction.</t>
+  </si>
+  <si>
+    <t>Is there any fee to access placement support?</t>
+  </si>
+  <si>
+    <t>Absolutely not. There is no need to pay anything for placement support.</t>
+  </si>
+  <si>
+    <t>How many job opportunities will be provided to each student?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You will get the maximum Placement support from Anudip till you do </t>
+  </si>
+  <si>
+    <t>Is there any mandate to relocate for each &amp; every job opportunity or we can get opportunity nearby location also?</t>
+  </si>
+  <si>
+    <t>Not at all. You can get the job at your nearby location also. But in some cases if the student stays at interior location &amp; has got the placement at Kolkata then it is not possible for the student to travel on daily basis. In that scenario student needs to relocate.</t>
+  </si>
+  <si>
+    <t>What kind of roles or industries will be offered to the students when they get placed?</t>
+  </si>
+  <si>
+    <t>Basically we provide the job at IT &amp; ITES industries. So you will get the job opportunity depending on the course which you have done from Anudip.</t>
+  </si>
+  <si>
+    <t>How does Anudip prepare students for placement interviews?</t>
+  </si>
+  <si>
+    <t>Anudip prepares students for job interviews by providing training in resume writing, communication skills, and mock interviews to build confidence and readiness. They may also offer industry-specific guidance, dress code tips, and connect students with potential employers for real-world exposure.</t>
+  </si>
+  <si>
+    <t>What kind of sectors hire through Anudip?</t>
+  </si>
+  <si>
+    <t>Anudip often helps to place individuals in sectors like healthcare, retail, hospitality, construction, manufacturing, financial, sales, BPO etc. which offer entry-level or skill-based jobs. These sectors value inclusive hiring and provide on-the-job training, making them ideal for supporting disadvantaged or marginalized job seekers.</t>
   </si>
 </sst>
 </file>
@@ -579,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6DEF95E-08A4-4BEB-913A-99C70BCF58D5}">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="113.1796875" bestFit="1" customWidth="1"/>
@@ -600,271 +738,455 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C3" s="1"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C8" s="1"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C9" s="1"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C11" s="1"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="C12" s="1"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C13" s="1"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C14" s="1"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C15" s="1"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B26" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>29</v>
+        <v>65</v>
+      </c>
+      <c r="B27" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>28</v>
+        <v>67</v>
+      </c>
+      <c r="B28" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>69</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>30</v>
+        <v>70</v>
+      </c>
+      <c r="B30" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>27</v>
+        <v>72</v>
+      </c>
+      <c r="B31" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+        <v>74</v>
+      </c>
+      <c r="B32" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="B33" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+      <c r="B34" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+        <v>80</v>
+      </c>
+      <c r="B35" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+      <c r="B36" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>84</v>
+      </c>
+      <c r="B37" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>86</v>
+      </c>
+      <c r="B38" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>87</v>
+      </c>
+      <c r="B39" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>89</v>
+      </c>
+      <c r="B40" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>95</v>
+      </c>
+      <c r="B43" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>97</v>
+      </c>
+      <c r="B44" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>99</v>
+      </c>
+      <c r="B45" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>101</v>
+      </c>
+      <c r="B46" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>103</v>
+      </c>
+      <c r="B47" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>105</v>
+      </c>
+      <c r="B48" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>107</v>
+      </c>
+      <c r="B49" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
